--- a/data/pack/eu/eurostat_fertiliser_input_index.xlsx
+++ b/data/pack/eu/eurostat_fertiliser_input_index.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Source: Eurostat (online data code: &lt;code&gt;). Adapted by dehesaindex.com where data are modified.</t>
+          <t>Source: Eurostat. Adapted by dehesaindex.com where data are modified.</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
